--- a/csvpp_manual/CSVPP設定と使い方.xlsx
+++ b/csvpp_manual/CSVPP設定と使い方.xlsx
@@ -1,40 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitwork\csvpp\csvpp_manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEFBB6FB-837C-4C87-B10C-79F117D3353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E07B7E1-A6B6-4013-B9EB-78A2C2EA7E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="405" windowWidth="21735" windowHeight="15030" tabRatio="858" activeTab="2" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" activeTab="3" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
   </bookViews>
   <sheets>
-    <sheet name="目次" sheetId="2" r:id="rId1"/>
-    <sheet name="はじめに" sheetId="28" r:id="rId2"/>
-    <sheet name="初期設定と使用方法" sheetId="36" r:id="rId3"/>
-    <sheet name="バージョンアップ履歴" sheetId="34" r:id="rId4"/>
+    <sheet name="はじめに" sheetId="28" r:id="rId1"/>
+    <sheet name="初期設定" sheetId="36" r:id="rId2"/>
+    <sheet name="初期設定2" sheetId="40" r:id="rId3"/>
+    <sheet name="CSVPPの実行方法" sheetId="37" r:id="rId4"/>
+    <sheet name="メニューウインドウ詳細" sheetId="39" r:id="rId5"/>
+    <sheet name="バージョンアップ履歴" sheetId="34" r:id="rId6"/>
   </sheets>
   <calcPr calcId="80000"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="311">
   <si>
     <t>内容</t>
     <rPh sb="0" eb="2">
@@ -54,26 +45,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>動作環境</t>
-    <rPh sb="0" eb="2">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カンキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>目次</t>
-    <rPh sb="0" eb="2">
-      <t>モクジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>バージョンアップ履歴</t>
-  </si>
-  <si>
     <t>バージョンアップ履歴</t>
     <rPh sb="8" eb="10">
       <t>リレキ</t>
@@ -97,65 +68,6 @@
   </si>
   <si>
     <t>CSVPPリリース</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>はじめに</t>
-  </si>
-  <si>
-    <t>言語仕様</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンゴ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コメント</t>
-  </si>
-  <si>
-    <t>変数の取り扱い</t>
-  </si>
-  <si>
-    <t>言語の書式</t>
-  </si>
-  <si>
-    <t>変数のスコープ</t>
-  </si>
-  <si>
-    <t>予約変数</t>
-  </si>
-  <si>
-    <t>配列</t>
-  </si>
-  <si>
-    <t>配列の応用</t>
-  </si>
-  <si>
-    <t>メソッド</t>
-  </si>
-  <si>
-    <t>分岐命令</t>
-  </si>
-  <si>
-    <t>ループ命令</t>
-  </si>
-  <si>
-    <t>コンソール表示</t>
-  </si>
-  <si>
-    <t>インクルード</t>
-  </si>
-  <si>
-    <t>文字列操作</t>
-  </si>
-  <si>
-    <t>エラーメッセージ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -187,10 +99,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>リファレンス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.02</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -202,16 +110,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>乱数発生</t>
-    <rPh sb="0" eb="2">
-      <t>ランスウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハッセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.03</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -255,16 +153,6 @@
     <t>％ｗｉｆ，％ｗｎｏｉｆ追加</t>
     <rPh sb="11" eb="13">
       <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>使用方法</t>
-    <rPh sb="0" eb="2">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ホウホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -362,10 +250,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メソッド2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.09</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -456,13 +340,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アスキーコード変換</t>
-    <rPh sb="7" eb="9">
-      <t>ヘンカン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.20a</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -478,82 +355,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>目次へ</t>
-    <rPh sb="0" eb="2">
-      <t>モクジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コマンド位置</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テキストファイルの読込み</t>
-  </si>
-  <si>
-    <t>継承</t>
-  </si>
-  <si>
-    <t>コンストラクタ</t>
-  </si>
-  <si>
-    <t>日付関連</t>
-  </si>
-  <si>
-    <t>ファイル制御関連</t>
-  </si>
-  <si>
-    <t>プログラム実行</t>
-  </si>
-  <si>
-    <t>コマンド一覧</t>
-  </si>
-  <si>
-    <t>予約変数</t>
-    <rPh sb="0" eb="2">
-      <t>ヨヤク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヘンスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>予約メソッド</t>
-    <rPh sb="0" eb="2">
-      <t>ヨヤク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特殊文字</t>
-    <rPh sb="0" eb="2">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>モジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>演算子</t>
-    <rPh sb="0" eb="3">
-      <t>エンザンシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>環境変数</t>
-    <rPh sb="0" eb="2">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヘンスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.21</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -677,23 +478,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ＣＳＶプリプロセッサ言語　ユーザーズマニュアル</t>
-    <rPh sb="10" eb="12">
-      <t>ゲンゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>２進数の扱い</t>
-    <rPh sb="1" eb="3">
-      <t>シンスウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>アツカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.27</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -959,16 +743,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>漢字コード変換</t>
-    <rPh sb="0" eb="2">
-      <t>カンジ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヘンカン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.47</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -988,13 +762,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>オブジェクトの生成</t>
-    <rPh sb="7" eb="9">
-      <t>セイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.49</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1050,16 +817,6 @@
     </rPh>
     <rPh sb="34" eb="36">
       <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>別名定義</t>
-    <rPh sb="0" eb="2">
-      <t>ベツメイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テイギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1278,25 +1035,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>配列内容のファイル保存、読み出し</t>
-    <rPh sb="0" eb="2">
-      <t>ハイレツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.61</t>
   </si>
   <si>
@@ -1314,16 +1052,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>値を返すメソッド</t>
-    <rPh sb="0" eb="1">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>-</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1359,13 +1087,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>URL、ファイル名解析</t>
-  </si>
-  <si>
-    <t>CSVファイルの読み書き</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.62a</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1501,19 +1222,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クラスの保存、読み出し</t>
-    <rPh sb="4" eb="6">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1.72</t>
   </si>
   <si>
@@ -1576,123 +1284,666 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ｃｓｖｐｐバージョン　:Ver 1.77</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ドキュメントバージョン:Ver 1.78</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>csvpp は、表計算ソフトで作成したデータを基に、各種プログラミング言語・スクリプト・バッチファイルへ自動変換するための インタプリタ型言語生成システム です。</t>
-  </si>
-  <si>
-    <t>ユーザーは CSV 形式で処理内容を記述し、csvpp がその定義に従って目的の言語コードを生成します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSVベースの言語定義  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">表計算ソフトとの高い親和性  </t>
-  </si>
-  <si>
-    <t>変換元となるデータも表計算ソフトで作成できるため、仕様作成からコード生成までを同一環境で完結できます。</t>
-  </si>
-  <si>
-    <t>仕様書を表計算ソフトで作成した場合、その内容をそのまま 言語コードやスクリプトへ変換 することができます。</t>
-  </si>
-  <si>
-    <t>仕様と実装の乖離を防ぎ、開発プロセスの効率化に寄与します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仕様書からの自動コード生成  </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>これにより、構造化されたデータ編集が容易になり、視覚的かつ直感的な設計が可能です。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OS:Windows 10,11</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>初期設定</t>
-  </si>
-  <si>
-    <t>「更新して終了」を押して、csvpp_ini.exeを終わらせると、csv.batが更新されます</t>
-    <rPh sb="1" eb="3">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>［スタート］→［プログラム］→［csvpp］ にある csvpp_ini を実行して初期設定を行います。</t>
-    <rPh sb="42" eb="44">
-      <t>ショキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>下記のウインドウが現れたら、赤丸の箇所を入力、もしくはチェックしてください。</t>
-    <rPh sb="0" eb="2">
-      <t>カキ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アラワ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>アカマル</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カショ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CSVPP を実行するには、CSVPP 用に作成した Excel ファイルを右クリックし、</t>
-  </si>
-  <si>
-    <t>「送る」→「csv」 を選択します。</t>
-  </si>
-  <si>
-    <t>この操作で DOS 画面が開き、ファイル内に記述された CSVPP 言語が順に実行されます。</t>
-  </si>
-  <si>
-    <t>Excel 上で作った内容をそのままコードとして動かせるのが特徴です。</t>
-  </si>
-  <si>
-    <t>従来のテキストエディタによるコーディングではなく、表計算ソフトを用いて言語を記述します。</t>
-    <rPh sb="35" eb="37">
-      <t>ゲンゴ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>キジュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>初期設定と使用方法</t>
   </si>
   <si>
     <t>マニュアルの見直し</t>
     <rPh sb="6" eb="8">
       <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Microsoft Excel</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>CSVPP は、表計算ソフトで作成したデータを基に、</t>
+  </si>
+  <si>
+    <t>各種プログラミング言語・スクリプト・バッチファイルへ自動変換するための</t>
+  </si>
+  <si>
+    <t>インタプリタ型言語生成システム です。</t>
+  </si>
+  <si>
+    <t>ユーザーは Excel ファイル上で処理内容を記述し、</t>
+  </si>
+  <si>
+    <t>CSVPP がその定義に従って目的の言語コードを生成します。</t>
+  </si>
+  <si>
+    <t>従来のテキストエディタによるコーディングではなく、</t>
+  </si>
+  <si>
+    <t>表計算ソフトを用いて言語仕様を記述します。</t>
+  </si>
+  <si>
+    <t>・セル単位で構造化されたデータ編集が可能</t>
+  </si>
+  <si>
+    <t>・視覚的・直感的な言語設計ができる</t>
+  </si>
+  <si>
+    <t>・設計と実装の整合性が高い</t>
+  </si>
+  <si>
+    <t>2．表計算ソフトとの高い親和性</t>
+  </si>
+  <si>
+    <t>変換元となるデータも Excel で作成できるため、</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仕様作成 → データ作成 → コード生成  </t>
+  </si>
+  <si>
+    <t>までを同一環境で完結できます。</t>
+  </si>
+  <si>
+    <t>1．Excel ベースの言語定義</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3．仕様書からの自動コード生成</t>
+  </si>
+  <si>
+    <t>仕様書を Excel で作成した場合、</t>
+  </si>
+  <si>
+    <t>その内容をそのまま 言語コードやスクリプトへ自動変換できます。</t>
+  </si>
+  <si>
+    <t>・仕様と実装の乖離を防止</t>
+  </si>
+  <si>
+    <t>・コード生成の自動化による作業効率化</t>
+  </si>
+  <si>
+    <t>・大規模プロジェクトでの品質向上に寄与</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動作環境</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Microsoft Windows 10 / 11</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>↓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダウンロードした CSVPP 一式を解凍します。</t>
+  </si>
+  <si>
+    <t>解凍したフォルダを ローカルディレクトリへ移動します。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>⚠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>注意</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：</t>
+  </si>
+  <si>
+    <t>OK → C:\csvpp</t>
+  </si>
+  <si>
+    <t>NG → C:\csv pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローカルディレクトリ名に空白（スペース）を含めてはいけません。  </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解凍したフォルダ内にある csvpp_menu.exe を起動します。</t>
+  </si>
+  <si>
+    <t>メニューウインドウ上で 右クリックし、</t>
+  </si>
+  <si>
+    <t>表示されたメニューから [csvpp_ini] を選択します。</t>
+  </si>
+  <si>
+    <t>画面下部の [更新して終了] ボタンを押します。</t>
+  </si>
+  <si>
+    <t>これにより、必要な設定ファイルが自動生成・更新されます。</t>
+  </si>
+  <si>
+    <t>初期設定が完了すると、</t>
+  </si>
+  <si>
+    <t>CSVPP の実行用バッチファイル csv.bat が更新されています。</t>
+  </si>
+  <si>
+    <t>フォルダ内にある csv.bat を確認し、</t>
+  </si>
+  <si>
+    <t>更新されていることをチェックしてください。</t>
+  </si>
+  <si>
+    <t>以上で CSVPP の初期設定は完了です。</t>
+  </si>
+  <si>
+    <t>マニュアルの修正</t>
+    <rPh sb="6" eb="8">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVPPの実行方法</t>
+  </si>
+  <si>
+    <t>起動すると、CSVPP のメニューウインドウが表示されます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これにより、CSVPP の初期設定画面が開きます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンソールウインドウの表示</t>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>console</t>
+  </si>
+  <si>
+    <t>表示されたメニューから [console] を選択</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVPP の処理ログを表示する コンソールウインドウが開きます。</t>
+  </si>
+  <si>
+    <t>CSVPP は Excel ファイルを入力として動作します。</t>
+  </si>
+  <si>
+    <t>ここでは例として filelist.xls を使用します。</t>
+  </si>
+  <si>
+    <t>CSVPP メニューウインドウ上に、</t>
+  </si>
+  <si>
+    <t>同じディレクトリにある filelist.xls をドラッグ＆ドロップします。</t>
+  </si>
+  <si>
+    <t>ドラッグ＆ドロップ後、</t>
+  </si>
+  <si>
+    <t>メニューウインドウ上に表示された filelist を右クリックし、</t>
+  </si>
+  <si>
+    <t>[excel] を選択します。</t>
+  </si>
+  <si>
+    <t>Excel が起動し、filelist.xls が開きます。</t>
+  </si>
+  <si>
+    <t>filelist.xls 内の 赤丸のセル（ディレクトリパス） を、</t>
+  </si>
+  <si>
+    <t>実際に存在するディレクトリパスへ書き換えます。</t>
+  </si>
+  <si>
+    <t>編集後、Excel を 保存します。</t>
+  </si>
+  <si>
+    <t>CSVPP メニューウインドウ上で、</t>
+  </si>
+  <si>
+    <t>filelist を ダブルクリックします。</t>
+  </si>
+  <si>
+    <t>filelist.xls が CSVPP により実行されます。</t>
+  </si>
+  <si>
+    <t>CSVPP 実行中は、コマンドプロンプトが表示され、</t>
+  </si>
+  <si>
+    <t>処理が完了すると Pause 状態になります。</t>
+  </si>
+  <si>
+    <t>適当なキーを押すと、コマンドプロンプトは閉じます。</t>
+  </si>
+  <si>
+    <t>CSVPP の実行結果は、</t>
+  </si>
+  <si>
+    <t>コンソールウインドウに表示されます。</t>
+  </si>
+  <si>
+    <t>CSVPPの実行方法（基本操作）</t>
+    <rPh sb="6" eb="8">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVPPの実行方法（簡易操作）</t>
+    <rPh sb="6" eb="8">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVPPメニューウインドウ詳細</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVPPメニューウインドウについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVプリプロセッサ（CSVPP）を簡単に実行するための メニューランチャーです。</t>
+  </si>
+  <si>
+    <t>Excel ファイルを右クリック →「送る → CSV」しなくてもよい</t>
+  </si>
+  <si>
+    <t>メニュー画面に ドラッグ＆ドロップするだけで登録</t>
+  </si>
+  <si>
+    <t>登録されたファイルを ダブルクリックするだけで CSVPP を実行</t>
+  </si>
+  <si>
+    <t>グループ分けが可能で、種類別に Excel ファイルを整理できる</t>
+  </si>
+  <si>
+    <t>CSVPP を日常的に使う場合、このメニューが最も効率的な起動方法になります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エクスプローラーのアドレスバーに shell:sendto を入れて、[送る]のフォルダを開いて、csv.batのショートカットをコピーして下さい。 </t>
+    <rPh sb="31" eb="32">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>クダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVPPの実行方法　その2（簡易操作）</t>
+    <rPh sb="6" eb="8">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csv.bat に filelist.xls をドラッグ＆ドロップすると、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>filelist.xls から右クリックして、[送る]→csv.batのショートカットを選択すると、</t>
+    <rPh sb="15" eb="16">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右側の操作ボタン一覧</t>
+  </si>
+  <si>
+    <t>ボタン</t>
+  </si>
+  <si>
+    <t>機能</t>
+  </si>
+  <si>
+    <t>メニューをタスクトレイに格納</t>
+  </si>
+  <si>
+    <t>ファイル項目を上に移動</t>
+  </si>
+  <si>
+    <t>ファイル項目を下に移動</t>
+  </si>
+  <si>
+    <t>ファイル項目を削除（複数選択可）</t>
+  </si>
+  <si>
+    <t>CSVPP を実行（複数選択可）</t>
+  </si>
+  <si>
+    <t>Excel で開く（複数選択可）</t>
+  </si>
+  <si>
+    <t>CSVPP の設定画面（csvpp_ini）を開く</t>
+  </si>
+  <si>
+    <t>コンソール出力ウインドウを開く</t>
+  </si>
+  <si>
+    <t>CSVPP のワークディレクトリ（c:\csv）を開く</t>
+  </si>
+  <si>
+    <t>↑</t>
+  </si>
+  <si>
+    <t>×</t>
+  </si>
+  <si>
+    <t>◎</t>
+  </si>
+  <si>
+    <t>ε</t>
+  </si>
+  <si>
+    <t>☆</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>dir</t>
+  </si>
+  <si>
+    <t>_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グループ機能</t>
+  </si>
+  <si>
+    <t>メニュー上部には現在の グループ名が表示されます。</t>
+  </si>
+  <si>
+    <t>Excel ファイルを種類別に整理する際に便利です。</t>
+  </si>
+  <si>
+    <t>・切り替え時、以前のグループは自動保存される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・∽ を押すとグループを切り替え</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>csvpp</t>
+  </si>
+  <si>
+    <t>CSVPP を実行</t>
+  </si>
+  <si>
+    <t>excel</t>
+  </si>
+  <si>
+    <t>Excel を起動</t>
+  </si>
+  <si>
+    <t>コンソールウインドウを開く</t>
+  </si>
+  <si>
+    <t>csvpp_ini</t>
+  </si>
+  <si>
+    <t>CSVPP の設定画面を開く</t>
+  </si>
+  <si>
+    <t>stay</t>
+  </si>
+  <si>
+    <t>メニューを常に最前面に表示</t>
+  </si>
+  <si>
+    <t>font</t>
+  </si>
+  <si>
+    <t>フォント変更</t>
+  </si>
+  <si>
+    <t>backcolor</t>
+  </si>
+  <si>
+    <t>背景色変更</t>
+  </si>
+  <si>
+    <t>csvpp work</t>
+  </si>
+  <si>
+    <t>c:\csv を開く</t>
+  </si>
+  <si>
+    <t>menu data dir</t>
+  </si>
+  <si>
+    <t>メニューデータのディレクトリを開く</t>
+  </si>
+  <si>
+    <t>excel dir</t>
+  </si>
+  <si>
+    <t>Excel ファイルのディレクトリを開く</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>プログラムのバージョン表示</t>
+  </si>
+  <si>
+    <t>右クリックメニュー</t>
+  </si>
+  <si>
+    <t>タスクトレイ動作</t>
+  </si>
+  <si>
+    <t>メニューをタスクトレイに格納した場合：</t>
+  </si>
+  <si>
+    <t>左クリック → メニューの表示／非表示を切り替え</t>
+  </si>
+  <si>
+    <t>右クリック → メニュー表示＋プログラム終了</t>
+  </si>
+  <si>
+    <t>生成されるファイル</t>
+  </si>
+  <si>
+    <t>csvpp_menu.exe と同じディレクトリに以下のファイルが生成されます：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">csvpp_menu.csv  </t>
+  </si>
+  <si>
+    <t>→ メニューの設定ファイル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">～##.csv  </t>
+  </si>
+  <si>
+    <t>→ グループごとの登録ファイル一覧</t>
+  </si>
+  <si>
+    <t>CSVPP の設定変更</t>
+  </si>
+  <si>
+    <t>CSVPP の動作環境を変更したい場合は以下のいずれかを行います：</t>
+  </si>
+  <si>
+    <t>・csv.bat を直接編集する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・csvpp_ini.exe を実行して設定し直す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期設定2</t>
+  </si>
+  <si>
+    <t>ExcelからCSVPPを実行したい時の初期設定になります。</t>
+    <rPh sb="13" eb="15">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>ショキセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示されたメニューから [excel_install] を選択します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上のボタンを押すと、Excelにアドインのタブが現れ、csvppの項目が現れます</t>
+    <rPh sb="0" eb="1">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加された「csvpp実行」はExcelファイルを保存して、CSVPP実行をします。</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「csvpp実行(close/open)」はExcelファイルを保存して、ファイルを閉じて、CSVPP実行をし、再び、Excelファイルを開きます。</t>
+    <rPh sb="6" eb="8">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>フタタ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ExcelからCSVPP実行</t>
+    <rPh sb="12" eb="14">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期設定2の設定をすると、ExcelからCSVPPができます。</t>
+    <rPh sb="0" eb="4">
+      <t>ショキセッテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アドイン」タブ→「csvpp」→[csvpp実行]</t>
+    <rPh sb="23" eb="25">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在、編集中のExcelファイルがCSVPP実行されます。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ヘンシュウチュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジッコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1701,7 +1952,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1712,12 +1963,6 @@
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1732,40 +1977,6 @@
       <b/>
       <sz val="14"/>
       <name val="HGP創英角ｺﾞｼｯｸUB"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="HG創英角ｺﾞｼｯｸUB"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="HG創英角ｺﾞｼｯｸUB"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="HG創英角ｺﾞｼｯｸUB"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="HG創英角ｺﾞｼｯｸUB"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="HG創英角ｺﾞｼｯｸUB"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -1799,32 +2010,22 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="ＭＳ Ｐ明朝"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="HGP創英角ｺﾞｼｯｸUB"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color indexed="12"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1861,26 +2062,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1898,34 +2087,19 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1949,96 +2123,242 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>72259</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>39414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>147821</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>9111</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33898" name="図 1">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E87A1EC3-ED84-B811-9766-633BA150589B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5DC0680-7AE3-45EF-94A9-8AEF9A898F4D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="314325" y="742950"/>
-          <a:ext cx="6896100" cy="5314950"/>
+          <a:off x="302173" y="1077311"/>
+          <a:ext cx="2486372" cy="1743318"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>177362</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>85397</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>81450</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>87130</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08F2710B-05B6-4C43-B1F2-81E1753867F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="407276" y="3685190"/>
+          <a:ext cx="2314898" cy="3010320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>203638</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>19707</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>504401</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>2388</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D0D0D9F-C57A-4890-916C-E32E0EC32A85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1478017" y="4604845"/>
+          <a:ext cx="1667108" cy="2991267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>98534</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>91965</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>360553</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>117209</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2610935-6380-4128-B144-A41199DBCC60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="328448" y="8473965"/>
+          <a:ext cx="8821381" cy="6725589"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>269327</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>65690</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>325836</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>57998</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D62F146-9BCF-4228-9C1C-F391A31E9B80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="499241" y="16133380"/>
+          <a:ext cx="2467319" cy="1371791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>82826</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>157370</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>492672</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>65690</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>8282</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>459827</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>65690</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="楕円 6">
+        <xdr:cNvPr id="17" name="四角形: 角を丸くする 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4DB6D63-519F-C165-1BDB-C727EBA1AC63}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59C51B81-D9F4-358B-9E51-96EF9EF85183}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2046,69 +2366,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="314739" y="2592457"/>
-          <a:ext cx="231913" cy="231913"/>
+          <a:off x="1767051" y="8171793"/>
+          <a:ext cx="650328" cy="197069"/>
         </a:xfrm>
-        <a:prstGeom prst="ellipse">
+        <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-        <a:effectLst/>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>338376</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>175955</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>570490</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>9292</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="楕円 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{210D967F-0095-C79F-4A43-D56D8A500A88}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="872705" y="2420138"/>
-          <a:ext cx="232114" cy="232922"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
@@ -2133,22 +2398,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>663619</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>157370</xdr:rowOff>
+      <xdr:colOff>315309</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>78827</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>208075</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>91965</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>105103</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="楕円 8">
+        <xdr:cNvPr id="18" name="四角形: 角を丸くする 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{881BF787-C603-507E-DFF2-17445643D7F9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CFA64DD-1A10-4897-A30E-07F162A90479}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2156,14 +2421,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1941363" y="2401553"/>
-          <a:ext cx="232114" cy="232922"/>
+          <a:off x="1589688" y="17841310"/>
+          <a:ext cx="1143001" cy="420414"/>
         </a:xfrm>
-        <a:prstGeom prst="ellipse">
+        <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
@@ -2185,25 +2450,162 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>72259</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>39414</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>100196</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9111</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74ABF417-39A0-4623-BDBE-CBDA88A1CD6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="510409" y="887139"/>
+          <a:ext cx="2494912" cy="1769922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>177362</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>85397</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>33825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>134755</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAFB38F4-DAC8-41B2-81B9-09FBDB14C65F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="405962" y="5971847"/>
+          <a:ext cx="2323438" cy="3049733"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>203638</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>19707</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>113876</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>50013</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC231231-0150-4376-811F-4A88ED4D2B9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1479988" y="6906282"/>
+          <a:ext cx="1672363" cy="3030681"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>82826</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>166663</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>121197</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>8282</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>199792</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>122841</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="楕円 9">
+        <xdr:cNvPr id="5" name="四角形: 角を丸くする 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{816E4DC5-C9E4-9619-2F6E-765CBD112F22}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EE78277-E1CF-4DBD-B925-D8713D7492EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2211,14 +2613,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="310497" y="2810431"/>
-          <a:ext cx="232114" cy="232922"/>
+          <a:off x="1530897" y="6115051"/>
+          <a:ext cx="859878" cy="256190"/>
         </a:xfrm>
-        <a:prstGeom prst="ellipse">
+        <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
@@ -2240,25 +2642,206 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>78180</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>134138</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>334449</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>29657</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E8A3543-E587-43EF-BAB1-4CAF6B4F448C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="390525" y="9525000"/>
+          <a:ext cx="7697274" cy="7754432"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>72259</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>39414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>310294</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>167267</xdr:rowOff>
+      <xdr:colOff>509771</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9111</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{250CED42-2844-4F9C-B037-8C551EE7E714}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="300859" y="2725464"/>
+          <a:ext cx="2494912" cy="1769922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>257498</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>9945</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1E048A8-087A-4C55-96E2-797CA4BDA269}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438150" y="4048125"/>
+          <a:ext cx="2314898" cy="3010320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>384941</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>119555</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>680449</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>110447</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED45E9B8-0199-42B1-A239-CB559BF0F8BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1508891" y="4967780"/>
+          <a:ext cx="1667108" cy="2991267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>673975</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>177691</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>638503</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>174735</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="楕円 10">
+        <xdr:cNvPr id="8" name="四角形: 角を丸くする 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D509927C-53AC-5852-D4DD-06653C339756}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0154FD66-1D56-4E31-AF12-E35DE89F4974}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2266,14 +2849,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2043582" y="2977699"/>
-          <a:ext cx="232114" cy="232922"/>
+          <a:off x="1797925" y="5425966"/>
+          <a:ext cx="650328" cy="197069"/>
         </a:xfrm>
-        <a:prstGeom prst="ellipse">
+        <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
@@ -2295,25 +2878,201 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>610735</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>67314</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E477872C-C044-4BD2-9F8B-713827378389}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="457200" y="8734425"/>
+          <a:ext cx="8135485" cy="4582164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>409817</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>66908</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99006734-C932-4319-9238-E9E03A16B627}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="485775" y="14849475"/>
+          <a:ext cx="1733792" cy="1667108"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>257498</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>420</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13D37A21-50D1-4F79-8842-92AEB01999C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438150" y="17040225"/>
+          <a:ext cx="2314898" cy="3010320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>371708</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>48042</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCE877E5-5A24-4F13-A068-83C4FA585CA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1885950" y="17706975"/>
+          <a:ext cx="1667108" cy="2991267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>491704</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>124845</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>723818</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>157975</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>307428</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>101819</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="楕円 11">
+        <xdr:cNvPr id="13" name="四角形: 角を丸くする 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5E73AD7-8B88-A70A-512C-F19B902CBD49}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD339E5E-56D4-4F51-AE14-92E910AF4BFC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2321,14 +3080,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1026033" y="3168199"/>
-          <a:ext cx="232114" cy="232922"/>
+          <a:off x="2152650" y="17954625"/>
+          <a:ext cx="650328" cy="197069"/>
         </a:xfrm>
-        <a:prstGeom prst="ellipse">
+        <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
@@ -2350,25 +3109,69 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>115833</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A97F5FA9-940B-4EED-B374-CC4E3D47E5C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438150" y="21850350"/>
+          <a:ext cx="8477250" cy="6716658"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>96765</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>152724</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>22221</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>185853</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="楕円 12">
+        <xdr:cNvPr id="16" name="四角形: 角を丸くする 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{637DEE16-3F22-9AC9-DD9C-BF9E2F4C627B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DACDD831-6DED-4940-BA9E-BC76CDF0866B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2376,14 +3179,14 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="324436" y="3395870"/>
-          <a:ext cx="232114" cy="232922"/>
+          <a:off x="1457325" y="24317325"/>
+          <a:ext cx="1352550" cy="228600"/>
         </a:xfrm>
-        <a:prstGeom prst="ellipse">
+        <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
@@ -2403,6 +3206,242 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>334857</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>181810</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{021B0A92-DCAA-4E7A-B95F-5B8975A1B874}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438150" y="30851475"/>
+          <a:ext cx="10621857" cy="5982535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>591685</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>181614</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5C0A912-38BF-45E6-86B2-1A4A01F27764}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438150" y="38252400"/>
+          <a:ext cx="8135485" cy="4582164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>205</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="四角形: 角を丸くする 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17F850AE-81B5-403F-A40D-3E08D107084E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="438150" y="41195625"/>
+          <a:ext cx="2933700" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>638498</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>190920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87C072F3-50D1-4781-A829-17F9662ED033}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4333875" y="2028825"/>
+          <a:ext cx="2314898" cy="3010320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28808</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>152817</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C18F249C-BD83-4C56-A55B-206E62C825D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4371975" y="5610225"/>
+          <a:ext cx="1667108" cy="2991267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2762,1448 +3801,1929 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D141A30-C245-4EB2-9726-7A3A7BF1DE0A}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C12DC13-CCC4-4651-A1B3-F12AA9B8F770}">
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.75" style="4" customWidth="1"/>
-    <col min="2" max="2" width="3.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="3.625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="61.5" style="4" customWidth="1"/>
-    <col min="5" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="11.875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="3.25" style="10" customWidth="1"/>
+    <col min="2" max="2" width="3.125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="68.125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="9" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="D2" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="D3" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B7" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B8" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="H11" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C12" s="18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C13" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C14" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C15" s="16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C16" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C17" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C18" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C19" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C20" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C21" s="18" t="s">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C22" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C23" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C24" s="18" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="9" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C25" s="16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C26" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C27" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C28" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C29" s="16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C30" s="16" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C17" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C18" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C21" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C22" s="9" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C31" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C32" s="15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B33" s="7"/>
-      <c r="C33" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B34" s="7"/>
-      <c r="C34" s="15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B35" s="7"/>
-      <c r="C35" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B36" s="7"/>
-      <c r="C36" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B37" s="7"/>
-      <c r="C37" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B38" s="7"/>
-      <c r="C38" s="15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B39" s="7"/>
-      <c r="C39" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B40" s="7"/>
-      <c r="C40" s="15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B41" s="7"/>
-      <c r="C41" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B42" s="7"/>
-      <c r="C42" s="15" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B43" s="7"/>
-      <c r="C43" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B45" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="C46" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B47" s="7"/>
-      <c r="C47" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="C48" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C49" s="19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C50" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C51" s="19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C52" s="19" t="s">
-        <v>83</v>
-      </c>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C23" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="13"/>
+      <c r="C26" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
+      <c r="C27" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C28" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C29" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C30" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="11"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="12"/>
+      <c r="C38" s="11"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C40" s="11"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C42" s="11"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C44" s="11"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C46" s="11"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="11"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="11"/>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="11"/>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C54" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="B7" location="はじめに!A1" display="はじめに" xr:uid="{B9BAE873-E7CD-4566-A903-8B26F3424022}"/>
-    <hyperlink ref="B9" location="バージョンアップ履歴!A1" display="バージョンアップ履歴" xr:uid="{7EB2A6D0-AB28-4142-BC0C-386E31ABCDAC}"/>
-    <hyperlink ref="C12" r:id="rId1" location="コマンド位置!A1" display="csvpp_manual2.xls - コマンド位置!A1" xr:uid="{5B227D1E-4127-48FA-903D-5AD87F87ED9A}"/>
-    <hyperlink ref="C13" r:id="rId2" location="コメント!A1" display="csvpp_manual2.xls - コメント!A1" xr:uid="{58CCB4D1-A58F-4706-AD8D-185F8A77E41A}"/>
-    <hyperlink ref="C14" r:id="rId3" location="変数の取り扱い!A1" display="csvpp_manual2.xls - 変数の取り扱い!A1" xr:uid="{C2D9FFD1-E577-4132-98C8-C90533E715FE}"/>
-    <hyperlink ref="C16" r:id="rId4" location="言語の書式!A1" display="csvpp_manual2.xls - 言語の書式!A1" xr:uid="{39B6B6D7-92F8-40AE-BE3C-D1A5ABEC3773}"/>
-    <hyperlink ref="C17" r:id="rId5" location="変数のスコープ!A1" display="csvpp_manual2.xls - 変数のスコープ!A1" xr:uid="{1B56F05A-B019-4260-821F-DB1EF8B63101}"/>
-    <hyperlink ref="C18" r:id="rId6" location="予約変数!A1" display="csvpp_manual2.xls - 予約変数!A1" xr:uid="{6EC26E1E-BE10-41EF-88CE-633C9AAFD626}"/>
-    <hyperlink ref="C19" r:id="rId7" location="配列!A1" display="csvpp_manual2.xls - 配列!A1" xr:uid="{49D6CBDC-9F5E-443D-8A63-DE63252AF3AE}"/>
-    <hyperlink ref="C20" r:id="rId8" location="配列の応用!A1" display="csvpp_manual2.xls - 配列の応用!A1" xr:uid="{B93EC9BC-5732-4AD1-BCB7-D2CC152CB63D}"/>
-    <hyperlink ref="C22" r:id="rId9" location="メソッド!A1" display="csvpp_manual2.xls - メソッド!A1" xr:uid="{4BCA958A-884D-4B68-B542-65F1C026D745}"/>
-    <hyperlink ref="C25" r:id="rId10" location="分岐命令!A1" display="csvpp_manual2.xls - 分岐命令!A1" xr:uid="{5133C98B-40AF-4CBA-8EA5-A3EFDA667481}"/>
-    <hyperlink ref="C26" r:id="rId11" location="ループ命令!A1" display="csvpp_manual2.xls - ループ命令!A1" xr:uid="{DBC222EC-B248-4C9A-925E-80AF2449FDE2}"/>
-    <hyperlink ref="C27" r:id="rId12" location="コンソール表示!A1" display="csvpp_manual2.xls - コンソール表示!A1" xr:uid="{2C453FC5-7B46-418F-8310-8D9FD03B0EFC}"/>
-    <hyperlink ref="C28" r:id="rId13" location="インクルード!A1" display="csvpp_manual2.xls - インクルード!A1" xr:uid="{378E57C1-044D-4749-990B-817401CA7966}"/>
-    <hyperlink ref="C29" r:id="rId14" location="テキストファイルの読込み!A1" display="csvpp_manual2.xls - テキストファイルの読込み!A1" xr:uid="{CF62F7CD-418C-4BF2-BB22-4EBB8E5D68D7}"/>
-    <hyperlink ref="C31" r:id="rId15" location="継承!A1" display="csvpp_manual2.xls - 継承!A1" xr:uid="{2F2E7EB5-84A2-4226-BA1F-462D53BB2B11}"/>
-    <hyperlink ref="C32" r:id="rId16" location="コンストラクタ!A1" display="csvpp_manual2.xls - コンストラクタ!A1" xr:uid="{4B03BDB9-9E83-48D7-979B-0CD845938DC7}"/>
-    <hyperlink ref="C33" r:id="rId17" location="別名定義!A1" xr:uid="{097B8895-E6C0-4E8B-8D3C-72CFA3732021}"/>
-    <hyperlink ref="C37" r:id="rId18" location="文字列操作!A1" display="csvpp_manual2.xls - 文字列操作!A1" xr:uid="{6AAD7749-D2BE-4351-94EB-28F222B35573}"/>
-    <hyperlink ref="C46" r:id="rId19" location="エラーメッセージ!A1" display="csvpp_manual3.xls - エラーメッセージ!A1" xr:uid="{04F00436-F7A5-405F-B342-259226DC6DEF}"/>
-    <hyperlink ref="C47" r:id="rId20" location="コマンド一覧!A1" display="csvpp_manual3.xls - コマンド一覧!A1" xr:uid="{A42CA63E-1CC8-42CF-AD00-831C793ADA5D}"/>
-    <hyperlink ref="C48" r:id="rId21" location="その他!A1" display="csvpp_manual3.xls - その他!A1" xr:uid="{211E7330-5C0D-437D-9453-3896E0AC0271}"/>
-    <hyperlink ref="C49" r:id="rId22" location="その他!A13" display="csvpp_manual3.xls - その他!A13" xr:uid="{35BA40D0-30A2-4FA4-9F12-47DFFE47CC25}"/>
-    <hyperlink ref="C50" r:id="rId23" location="その他!A20" display="csvpp_manual3.xls - その他!A20" xr:uid="{9E710C6F-CB36-49D2-9076-08021AB10FBE}"/>
-    <hyperlink ref="C51" r:id="rId24" location="その他!A37" display="csvpp_manual3.xls - その他!A37" xr:uid="{8B724783-4350-4C83-86AF-762FD42B1DA2}"/>
-    <hyperlink ref="C52" r:id="rId25" location="その他!A59" display="csvpp_manual3.xls - その他!A59" xr:uid="{4AD64070-DBB0-455E-8EC1-A9183DB9F073}"/>
-    <hyperlink ref="C35" r:id="rId26" location="ファイル制御関連!A1" display="csvpp_manual2.xls - ファイル制御関連!A1" xr:uid="{FB989420-AEE3-4940-8C04-D7E5C24C9BDA}"/>
-    <hyperlink ref="C34" r:id="rId27" location="日付関連!A1" display="csvpp_manual2.xls - 日付関連!A1" xr:uid="{D9E61EF5-10FA-4DE2-8099-5C7F1F8A6380}"/>
-    <hyperlink ref="C38" r:id="rId28" location="プログラム実行!A1" display="csvpp_manual2.xls - プログラム実行!A1" xr:uid="{CD2DFCA7-08C3-4384-BBB6-F809ED3DCF7F}"/>
-    <hyperlink ref="C39" r:id="rId29" location="乱数発生!A1" display="csvpp_manual2.xls - 乱数発生!A1" xr:uid="{631E408C-D2D1-4C12-A9FA-32583B85E14E}"/>
-    <hyperlink ref="C23" r:id="rId30" location="メソッド2!A1" display="csvpp_manual2.xls - メソッド2!A1" xr:uid="{4F8AA2FC-AA93-4C13-B360-ABB337CE4261}"/>
-    <hyperlink ref="C40" r:id="rId31" location="アスキーコード変換!A1" display="csvpp_manual2.xls - アスキーコード変換!A1" xr:uid="{FE9FEE41-0C06-4EBF-9A84-2A227BF842C8}"/>
-    <hyperlink ref="C15" r:id="rId32" location="２進数の扱い!A1" xr:uid="{E2841115-B8B6-4255-9469-A6162C669D25}"/>
-    <hyperlink ref="C41" r:id="rId33" location="漢字コード変換!A1" xr:uid="{E7FA20F1-E434-4DE6-A613-B4F4985B276D}"/>
-    <hyperlink ref="C42" r:id="rId34" location="オブジェクトの生成!A1" xr:uid="{436749BE-CD83-4B5C-84C5-FC07B1D5E387}"/>
-    <hyperlink ref="C30" r:id="rId35" location="CSVファイルの読み書き!A1" xr:uid="{1B1B55D5-CA04-4D82-AE5D-E1C7B494A2C8}"/>
-    <hyperlink ref="C24" r:id="rId36" location="値を返すメソッド!A1" xr:uid="{7E178FFD-C598-4647-8CA7-1BE3AD2A59F4}"/>
-    <hyperlink ref="C36" r:id="rId37" location="URLファイル名解析!A1" xr:uid="{72EE1E00-5B5D-4F93-B27E-8681BEB2C1AF}"/>
-    <hyperlink ref="C43" r:id="rId38" location="オブジェクトの生成!A1" display="オブジェクトの生成" xr:uid="{27906571-2433-4277-B038-E335A0039D95}"/>
-    <hyperlink ref="B8" location="初期設定と使用方法!A1" display="初期設定と使用方法" xr:uid="{BB15D430-16A7-4665-BBDA-7B6D0AEB876E}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="76" orientation="portrait" verticalDpi="300" r:id="rId39"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C12DC13-CCC4-4651-A1B3-F12AA9B8F770}">
-  <dimension ref="A1:L49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABCAAC1F-4B16-49AF-B77F-A0E51A8B3C0E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.25" style="31" customWidth="1"/>
-    <col min="2" max="2" width="3.25" style="26" customWidth="1"/>
-    <col min="3" max="3" width="68.125" style="25" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="3" style="9" customWidth="1"/>
+    <col min="2" max="2" width="4" style="9" customWidth="1"/>
+    <col min="3" max="3" width="9.75" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="22"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="23"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="23"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="24"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="28" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C9" s="25" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C10" s="25" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="28" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C13" s="25" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C16" s="25" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C17" s="25" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="22"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C24" s="27"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C27" s="27"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="29"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C31" s="27"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="27"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="27"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="27"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C39" s="27"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C41" s="27"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C43" s="27"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C45" s="27"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C47" s="27"/>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C49" s="27"/>
+    <row r="1" spans="1:10" s="8" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" s="8" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" s="8" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="10"/>
+      <c r="B3" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="1:10" s="8" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="10"/>
+      <c r="B4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:10" s="8" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:10" s="8" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="10"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C7" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C8" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C9" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="8" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="10"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="9" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C91" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C92" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C93" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C94" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C95" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C105" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="9" t="s">
+        <v>196</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="A33" r:id="rId1" location="目次!A1" display="csvpp_manual1.xls - 目次!A1" xr:uid="{E49B03ED-6B82-4BD5-84D9-D839130ED8E9}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="77" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABCAAC1F-4B16-49AF-B77F-A0E51A8B3C0E}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC112017-FA93-4849-9715-6ED7B9F18ABD}">
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr defaultColWidth="4.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="23" customWidth="1"/>
-    <col min="2" max="2" width="4" style="23" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="23" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="23"/>
+    <col min="1" max="1" width="4.625" style="10"/>
+    <col min="2" max="16384" width="4.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="22" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
-        <v>214</v>
+    <row r="1" spans="1:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="23" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" s="22" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A34" s="22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="23" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="23" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="23" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="26"/>
+      <c r="B3" s="9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="9" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="9" t="s">
+        <v>306</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="A41" r:id="rId1" location="目次!A1" display="csvpp_manual1.xls - 目次!A1" xr:uid="{DC6177DE-A2BA-44DA-85D0-F6CCF42C0371}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="77" orientation="portrait" horizontalDpi="4294967293" r:id="rId2"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E8133D-E54E-4B41-9AF5-5427E1ADDEA6}">
+  <dimension ref="A1:B234"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.75" style="10" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B224" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B225" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B228" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B229" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B232" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B233" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B234" s="9" t="s">
+        <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B062E8E7-EFB1-4A27-947E-B15CF2E85DF1}">
+  <dimension ref="A1:C59"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.75" style="10" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="9" customWidth="1"/>
+    <col min="3" max="3" width="38.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="9" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="9" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC7C10D-459D-4561-9FA8-BECF1E2769A1}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
-    <col min="2" max="2" width="15.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.5" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.5" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" s="11" t="s">
+      <c r="B4" s="5">
+        <v>36934</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="11" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" s="12" t="s">
+      <c r="B5" s="5">
+        <v>36966</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="13">
-        <v>36934</v>
-      </c>
-      <c r="C4" s="12" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A5" s="12" t="s">
+      <c r="B6" s="5">
+        <v>36996</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5">
+        <v>37067</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5">
+        <v>37075</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="5">
+        <v>37158</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="5">
+        <v>37161</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="5">
+        <v>37318</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="5">
+        <v>37332</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="5">
+        <v>37443</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="5">
+        <v>37445</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="13">
-        <v>36966</v>
-      </c>
-      <c r="C5" s="14" t="s">
+      <c r="B15" s="5">
+        <v>37680</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" s="12" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>37759</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="13">
-        <v>36996</v>
-      </c>
-      <c r="C6" s="12" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7" s="12" t="s">
+      <c r="B17" s="5">
+        <v>37766</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="13">
-        <v>37067</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B18" s="5">
+        <v>37820</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A8" s="12" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="13">
-        <v>37075</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="B19" s="5">
+        <v>37849</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A9" s="12" t="s">
+    <row r="20" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A20" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="13">
-        <v>37158</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="B20" s="5">
+        <v>37858</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A10" s="12" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="13">
-        <v>37161</v>
-      </c>
-      <c r="C10" s="12" t="s">
+      <c r="B21" s="5">
+        <v>37886</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A11" s="12" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5">
+        <v>37899</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="13">
-        <v>37318</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="B23" s="5">
+        <v>37930</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A12" s="12" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="13">
-        <v>37332</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B24" s="5">
+        <v>38038</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A13" s="12" t="s">
+    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="13">
-        <v>37443</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="B25" s="5">
+        <v>38122</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A14" s="12" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A26" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="13">
-        <v>37445</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="B26" s="5">
+        <v>38123</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A15" s="12" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="13">
-        <v>37680</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="B27" s="5">
+        <v>38454</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A16" s="12" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="13">
-        <v>37759</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="B28" s="5">
+        <v>38487</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A17" s="12" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="5">
+        <v>38689</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="13">
-        <v>37766</v>
-      </c>
-      <c r="C17" s="14" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A30" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A18" s="12" t="s">
+      <c r="B30" s="5">
+        <v>38914</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="13">
-        <v>37820</v>
-      </c>
-      <c r="C18" s="14" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A31" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A19" s="12" t="s">
+      <c r="B31" s="5">
+        <v>39408</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="13">
-        <v>37849</v>
-      </c>
-      <c r="C19" s="14" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A32" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A20" s="12" t="s">
+      <c r="B32" s="5">
+        <v>39508</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="13">
-        <v>37858</v>
-      </c>
-      <c r="C20" s="14" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A21" s="12" t="s">
+      <c r="B33" s="5">
+        <v>39751</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="13">
-        <v>37886</v>
-      </c>
-      <c r="C21" s="14" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A22" s="12" t="s">
+      <c r="B34" s="5">
+        <v>39754</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A35" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="13">
-        <v>37899</v>
-      </c>
-      <c r="C22" s="14" t="s">
+      <c r="B35" s="5">
+        <v>39778</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A36" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="5">
+        <v>39886</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="5">
+        <v>39919</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A38" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="5">
+        <v>40012</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5">
+        <v>40018</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="5">
+        <v>40257</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A41" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="5">
+        <v>40258</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A42" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="5">
+        <v>40258</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="5">
+        <v>40382</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A44" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="5">
+        <v>40488</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A45" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="5">
+        <v>40496</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="5">
+        <v>40571</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A47" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="5">
+        <v>40579</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5">
+        <v>40579</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="54" x14ac:dyDescent="0.15">
+      <c r="A49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="5">
+        <v>40600</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A50" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="5">
+        <v>40608</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A51" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="5">
+        <v>40638</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A52" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="5">
+        <v>40657</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A53" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="5">
+        <v>40657</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A54" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="5">
+        <v>40663</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A55" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="5">
+        <v>40673</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A56" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" s="5">
+        <v>40706</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A23" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="13">
-        <v>37930</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A24" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="13">
-        <v>38038</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A25" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="13">
-        <v>38122</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A26" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="13">
-        <v>38123</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A27" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" s="13">
-        <v>38454</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A28" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" s="13">
-        <v>38487</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A29" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="13">
-        <v>38689</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A30" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" s="13">
-        <v>38914</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A31" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="13">
-        <v>39408</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A32" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" s="13">
-        <v>39508</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A33" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="13">
-        <v>39751</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A34" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="13">
-        <v>39754</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A35" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="13">
-        <v>39778</v>
-      </c>
-      <c r="C35" s="14" t="s">
+    <row r="57" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A57" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A36" s="12" t="s">
+      <c r="B57" s="5">
+        <v>40846</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="13">
-        <v>39886</v>
-      </c>
-      <c r="C36" s="14" t="s">
+    </row>
+    <row r="58" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A58" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A37" s="12" t="s">
+      <c r="B58" s="5">
+        <v>40906</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B37" s="13">
-        <v>39919</v>
-      </c>
-      <c r="C37" s="14" t="s">
+    </row>
+    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A59" s="4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A38" s="12" t="s">
+      <c r="B59" s="5">
+        <v>40916</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B38" s="13">
-        <v>40012</v>
-      </c>
-      <c r="C38" s="14" t="s">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A60" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13">
-        <v>40018</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="B60" s="5">
+        <v>40917</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A40" s="12" t="s">
+    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A61" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="13">
-        <v>40257</v>
-      </c>
-      <c r="C40" s="14" t="s">
+      <c r="B61" s="5">
+        <v>40922</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A41" s="12" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A62" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B41" s="13">
-        <v>40258</v>
-      </c>
-      <c r="C41" s="14" t="s">
+      <c r="B62" s="5">
+        <v>40922</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A42" s="12" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A63" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B42" s="13">
-        <v>40258</v>
-      </c>
-      <c r="C42" s="14" t="s">
+      <c r="B63" s="5">
+        <v>40943</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A43" s="12" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A64" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="5">
+        <v>40976</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B43" s="13">
-        <v>40382</v>
-      </c>
-      <c r="C43" s="14" t="s">
+    </row>
+    <row r="65" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A65" s="4" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A44" s="12" t="s">
+      <c r="B65" s="5">
+        <v>40979</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B44" s="13">
-        <v>40488</v>
-      </c>
-      <c r="C44" s="14" t="s">
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A66" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A45" s="12" t="s">
+      <c r="B66" s="5">
+        <v>40986</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A67" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B45" s="13">
-        <v>40496</v>
-      </c>
-      <c r="C45" s="14" t="s">
+      <c r="B67" s="5">
+        <v>40988</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A46" s="12" t="s">
+    <row r="68" spans="1:3" ht="27" x14ac:dyDescent="0.15">
+      <c r="A68" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B46" s="13">
-        <v>40571</v>
-      </c>
-      <c r="C46" s="14" t="s">
+      <c r="B68" s="5">
+        <v>41051</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A47" s="12" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A69" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="13">
-        <v>40579</v>
-      </c>
-      <c r="C47" s="14" t="s">
+      <c r="B69" s="5">
+        <v>41267</v>
+      </c>
+      <c r="C69" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13">
-        <v>40579</v>
-      </c>
-      <c r="C48" s="14" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A70" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="5">
+        <v>41399</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="54" x14ac:dyDescent="0.15">
-      <c r="A49" s="12" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A71" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="5">
+        <v>41622</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B49" s="13">
-        <v>40600</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A50" s="12" t="s">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A72" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B50" s="13">
-        <v>40608</v>
-      </c>
-      <c r="C50" s="14" t="s">
+      <c r="B72" s="5">
+        <v>41643</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A51" s="12" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A73" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="5">
+        <v>41647</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B51" s="13">
-        <v>40638</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A52" s="12" t="s">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A74" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="5">
+        <v>41657</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A75" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B52" s="13">
-        <v>40657</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A53" s="12" t="s">
+      <c r="B75" s="5">
+        <v>41796</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B53" s="13">
-        <v>40657</v>
-      </c>
-      <c r="C53" s="14" t="s">
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A76" s="4" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A54" s="12" t="s">
+      <c r="B76" s="5">
+        <v>41812</v>
+      </c>
+      <c r="C76" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B54" s="13">
-        <v>40663</v>
-      </c>
-      <c r="C54" s="14" t="s">
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A77" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A55" s="12" t="s">
+      <c r="B77" s="5">
+        <v>42224</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B55" s="13">
-        <v>40673</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A56" s="12" t="s">
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A78" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="5">
+        <v>46235</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B56" s="13">
-        <v>40706</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A57" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B57" s="13">
-        <v>40846</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A58" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B58" s="13">
-        <v>40906</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A59" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B59" s="13">
-        <v>40916</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A60" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B60" s="13">
-        <v>40917</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A61" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B61" s="13">
-        <v>40922</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A62" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B62" s="13">
-        <v>40922</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A63" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B63" s="13">
-        <v>40943</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A64" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B64" s="13">
-        <v>40976</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A65" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B65" s="13">
-        <v>40979</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A66" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B66" s="13">
-        <v>40986</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A67" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B67" s="13">
-        <v>40988</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A68" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="B68" s="13">
-        <v>41051</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A69" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B69" s="13">
-        <v>41267</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A70" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B70" s="13">
-        <v>41399</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A71" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B71" s="13">
-        <v>41622</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A72" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B72" s="13">
-        <v>41643</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A73" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="B73" s="13">
-        <v>41647</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A74" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B74" s="13">
-        <v>41657</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A75" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B75" s="13">
-        <v>41796</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A76" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B76" s="13">
-        <v>41812</v>
-      </c>
-      <c r="C76" s="14" t="s">
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A79" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B79" s="5">
+        <v>46254</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A77" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B77" s="13">
-        <v>42224</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A78" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B78" s="13">
-        <v>46235</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A80" s="17" t="s">
-        <v>70</v>
-      </c>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A81" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="A80" r:id="rId1" location="目次!A1" display="csvpp_manual1.xls - 目次!A1" xr:uid="{7ACA0187-D904-4AD6-99B9-5AE5E93E9A0E}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="60" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="60" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>